--- a/education_forms/038_math_department_student_feedback_for_teachers--education_forms.xlsx
+++ b/education_forms/038_math_department_student_feedback_for_teachers--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>teacher_performance_2</t>
+          <t>teacher_performance_repeated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teacher Performance</t>
+          <t>Teacher Performance (Again)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>course_content_2</t>
+          <t>course_content_repeated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Course Content</t>
+          <t>Course Content (Again)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>overall_experience_2</t>
+          <t>overall_experience_repeated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall Experience</t>
+          <t>Overall Experience (Again)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -769,7 +769,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>overall_experience_2_choices</t>
+          <t>overall_experience_repeated_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overall_experience_2_choices</t>
+          <t>overall_experience_repeated_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
